--- a/Docs/Three In A Row - Audio Script.xlsx
+++ b/Docs/Three In A Row - Audio Script.xlsx
@@ -484,7 +484,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Tapu and his puppy friend are having a game day! Let's play!</t>
+          <t>Tapu and his pet friend are having a game day! Let's play!</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Hmm, the puppy is thinking!</t>
+          <t>Hmm, the pet is thinking!</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>What will the puppy do?</t>
+          <t>What will the pet do?</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Oh! The puppy has two in a row! Can you stop it?</t>
+          <t>Oh! The pet has two in a row! Can you stop it?</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Careful! Put your face in the square to stop the puppy!</t>
+          <t>Careful! Put your face in the square to stop the pet!</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Fantastic! You beat the puppy! Great thinking!</t>
+          <t>Fantastic! You beat the pet! Great thinking!</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>The puppy got three in a row! Let's try again, you can do it!</t>
+          <t>The pet got three in a row! Let's try again, you can do it!</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1056,7 +1056,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Almost! Watch the puppy's faces and try again. You are getting better!</t>
+          <t>Almost! Watch the pet's faces and try again. You are getting better!</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>A tie! Tapu and the puppy both did so well! Let's go again!</t>
+          <t>A tie! Tapu and the pet both did so well! Let's go again!</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
